--- a/Data/Home/BedroomOne.HumanState.xlsx
+++ b/Data/Home/BedroomOne.HumanState.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H203"/>
+  <dimension ref="A1:I203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709251537</v>
+        <v>1711843725</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709252545</v>
+        <v>1711845215</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709253342</v>
+        <v>1711846060</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,7 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +591,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709281703</v>
+        <v>1711895068</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +605,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +624,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709284272</v>
+        <v>1711898793</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -629,6 +638,7 @@
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709284728</v>
+        <v>1711899499</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +671,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +690,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709245196</v>
+        <v>1711929078</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +704,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +723,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709246250</v>
+        <v>1711930386</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -725,6 +737,7 @@
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +756,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709246896</v>
+        <v>1711931364</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +770,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +789,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709280555</v>
+        <v>1711976020</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +803,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +822,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709283065</v>
+        <v>1711979160</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +836,7 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +855,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709283572</v>
+        <v>1711979907</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +869,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +888,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709331258</v>
+        <v>1712016214</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +902,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +921,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709332407</v>
+        <v>1712017628</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +935,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +954,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709333024</v>
+        <v>1712018477</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +968,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +987,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709365455</v>
+        <v>1712056599</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1001,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1020,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709368121</v>
+        <v>1712059807</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1034,7 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1053,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709368712</v>
+        <v>1712060397</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1067,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1086,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709417816</v>
+        <v>1712102717</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1077,6 +1100,7 @@
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1119,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709418873</v>
+        <v>1712104285</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1109,6 +1133,7 @@
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1152,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709419506</v>
+        <v>1712105138</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1166,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1185,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709428510</v>
+        <v>1712115930</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1199,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1218,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709432454</v>
+        <v>1712121043</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1232,11 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1255,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709459169</v>
+        <v>1712145424</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1269,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1288,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709461940</v>
+        <v>1712148849</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1302,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1321,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709462507</v>
+        <v>1712149591</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1335,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1354,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709503504</v>
+        <v>1712189077</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1333,6 +1368,7 @@
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1387,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709504563</v>
+        <v>1712190348</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1365,6 +1401,7 @@
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1420,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709505250</v>
+        <v>1712191429</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1434,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1453,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709539799</v>
+        <v>1712203751</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1429,6 +1467,7 @@
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709542299</v>
+        <v>1712208019</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1500,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1519,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709542939</v>
+        <v>1712222833</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1493,6 +1533,7 @@
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1552,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709590046</v>
+        <v>1712226377</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1525,6 +1566,7 @@
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1585,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709591343</v>
+        <v>1712226981</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1599,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1618,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709592135</v>
+        <v>1712275238</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1589,6 +1632,7 @@
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1651,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709602612</v>
+        <v>1712276741</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1621,6 +1665,7 @@
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1684,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709606144</v>
+        <v>1712277750</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1698,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1717,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709625856</v>
+        <v>1712313124</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1685,6 +1731,7 @@
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1750,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709628121</v>
+        <v>1712316601</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1717,6 +1764,7 @@
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1783,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709628573</v>
+        <v>1712317264</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1797,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1816,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709681016</v>
+        <v>1712364659</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1781,6 +1830,7 @@
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1849,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709684462</v>
+        <v>1712369276</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1813,6 +1863,7 @@
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1882,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709685627</v>
+        <v>1712370309</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1896,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1915,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709687553</v>
+        <v>1712372552</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1877,6 +1929,7 @@
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1948,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709699217</v>
+        <v>1712379573</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1909,6 +1962,7 @@
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +1981,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709712802</v>
+        <v>1712395818</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +1995,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2014,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709716582</v>
+        <v>1712399867</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1973,6 +2028,7 @@
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2047,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709717151</v>
+        <v>1712400436</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2005,6 +2061,7 @@
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2080,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709766849</v>
+        <v>1712451515</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2094,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2113,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709776327</v>
+        <v>1712462167</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2069,6 +2127,7 @@
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2146,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709777158</v>
+        <v>1712463675</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2101,6 +2160,7 @@
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2179,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709778707</v>
+        <v>1712465969</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2193,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2212,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709786344</v>
+        <v>1712472487</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2226,11 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2249,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709797532</v>
+        <v>1712500305</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2263,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2282,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709800600</v>
+        <v>1712505497</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2296,11 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2319,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709801134</v>
+        <v>1712506211</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2333,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2352,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709850159</v>
+        <v>1712534729</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2293,6 +2366,7 @@
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2385,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709851313</v>
+        <v>1712536247</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2325,6 +2399,7 @@
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2418,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709851891</v>
+        <v>1712537204</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2432,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2451,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709876865</v>
+        <v>1712566064</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2389,6 +2465,7 @@
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2484,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709879246</v>
+        <v>1712569247</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2421,6 +2498,7 @@
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2517,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709879709</v>
+        <v>1712569844</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2531,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2550,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709937593</v>
+        <v>1712620732</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2485,6 +2564,7 @@
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2583,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709938602</v>
+        <v>1712622145</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2517,6 +2597,7 @@
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2616,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709939196</v>
+        <v>1712623234</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2630,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2649,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709971241</v>
+        <v>1712635777</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2581,6 +2663,7 @@
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2682,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709974056</v>
+        <v>1712640079</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2613,6 +2696,7 @@
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2715,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709974664</v>
+        <v>1712664971</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2729,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2748,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710023510</v>
+        <v>1712668286</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2677,6 +2762,7 @@
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2781,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710024741</v>
+        <v>1712668904</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2709,6 +2795,7 @@
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2814,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710025420</v>
+        <v>1712707339</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2828,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2847,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710033989</v>
+        <v>1712708799</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2773,6 +2861,7 @@
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2880,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710037756</v>
+        <v>1712709758</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2894,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2913,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710055408</v>
+        <v>1712760089</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2837,6 +2927,7 @@
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2946,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710057883</v>
+        <v>1712763234</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2869,6 +2960,7 @@
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +2979,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710058386</v>
+        <v>1712763874</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +2993,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3012,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710108356</v>
+        <v>1712792741</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2933,6 +3026,7 @@
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3045,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710109486</v>
+        <v>1712794236</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2965,6 +3059,7 @@
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3078,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710110105</v>
+        <v>1712795144</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3092,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3111,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710132720</v>
+        <v>1712828843</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3029,6 +3125,7 @@
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3144,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710135231</v>
+        <v>1712831877</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3061,6 +3158,7 @@
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3177,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710135747</v>
+        <v>1712832551</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3191,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3210,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710197387</v>
+        <v>1712879108</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3125,6 +3224,7 @@
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3243,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710198626</v>
+        <v>1712880531</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3157,6 +3257,7 @@
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3276,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710199443</v>
+        <v>1712881457</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3290,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3309,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710240102</v>
+        <v>1712919955</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3221,6 +3323,7 @@
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3342,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710242801</v>
+        <v>1712923361</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3253,6 +3356,7 @@
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3375,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710243425</v>
+        <v>1712924025</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3389,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3408,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710287696</v>
+        <v>1712970224</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3317,6 +3422,7 @@
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3441,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710296116</v>
+        <v>1712980586</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3349,6 +3455,7 @@
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3474,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710297111</v>
+        <v>1712981673</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3488,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3507,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710299135</v>
+        <v>1712983846</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3413,6 +3521,7 @@
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3540,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710307982</v>
+        <v>1712996134</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3445,6 +3554,7 @@
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3573,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710322796</v>
+        <v>1713014383</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3587,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3606,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710326150</v>
+        <v>1713019231</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3509,6 +3620,7 @@
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3639,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710326649</v>
+        <v>1713019891</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3541,6 +3653,7 @@
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3672,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710372686</v>
+        <v>1713056623</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3686,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3705,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710376484</v>
+        <v>1713066832</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3605,6 +3719,7 @@
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3738,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710377522</v>
+        <v>1713068093</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3637,6 +3752,7 @@
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3771,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710379482</v>
+        <v>1713070326</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3785,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3804,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710389776</v>
+        <v>1713082756</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3701,6 +3818,7 @@
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3837,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710403054</v>
+        <v>1713103319</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3733,6 +3851,7 @@
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3870,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710406214</v>
+        <v>1713107956</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3884,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3903,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710406693</v>
+        <v>1713108566</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3797,6 +3917,7 @@
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3936,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710456408</v>
+        <v>1713139345</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +3950,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +3969,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710457784</v>
+        <v>1713140857</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3861,6 +3983,7 @@
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4002,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710458644</v>
+        <v>1713141882</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3893,6 +4016,7 @@
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4035,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710491422</v>
+        <v>1713153463</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4049,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4068,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710493970</v>
+        <v>1713158919</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3957,6 +4082,11 @@
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4105,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710494513</v>
+        <v>1713172615</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3989,6 +4119,7 @@
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4138,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710541291</v>
+        <v>1713175697</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4152,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4171,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710542302</v>
+        <v>1713176333</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4053,6 +4185,7 @@
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4204,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710543046</v>
+        <v>1713225538</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4085,6 +4218,7 @@
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4237,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710551371</v>
+        <v>1713226982</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4251,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4270,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710555145</v>
+        <v>1713227955</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4149,6 +4284,7 @@
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4303,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710575614</v>
+        <v>1713263559</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4181,6 +4317,7 @@
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4336,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710578221</v>
+        <v>1713266835</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4350,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4369,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710578869</v>
+        <v>1713267472</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4245,6 +4383,7 @@
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4402,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710627650</v>
+        <v>1713311769</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4277,6 +4416,7 @@
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4435,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710628569</v>
+        <v>1713313340</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4449,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4468,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710629272</v>
+        <v>1713314339</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4482,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4501,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710654914</v>
+        <v>1713351770</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4515,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4534,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710657215</v>
+        <v>1713355072</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4548,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4567,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710657778</v>
+        <v>1713355734</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4581,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4600,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710714580</v>
+        <v>1713397954</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4469,6 +4614,7 @@
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4633,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710715747</v>
+        <v>1713399322</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4501,6 +4647,7 @@
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4666,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710716498</v>
+        <v>1713400190</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4680,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4699,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710726514</v>
+        <v>1713443643</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4565,6 +4713,7 @@
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4732,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710731327</v>
+        <v>1713446675</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4597,6 +4746,7 @@
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4765,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710753226</v>
+        <v>1713447290</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4779,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4798,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710755642</v>
+        <v>1713484901</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4812,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4831,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710756271</v>
+        <v>1713486270</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4845,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4864,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710800709</v>
+        <v>1713487086</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4878,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4897,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710801792</v>
+        <v>1713525740</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4911,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4930,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710802435</v>
+        <v>1713529319</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4789,6 +4944,7 @@
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +4963,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710832593</v>
+        <v>1713529886</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4821,6 +4977,7 @@
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +4996,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710835092</v>
+        <v>1713574882</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5010,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5029,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710835691</v>
+        <v>1713580576</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4885,6 +5043,7 @@
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5062,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710888818</v>
+        <v>1713581788</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4917,6 +5076,7 @@
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5095,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710892331</v>
+        <v>1713584186</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5109,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5128,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710893358</v>
+        <v>1713598770</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4981,6 +5142,7 @@
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5161,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710895260</v>
+        <v>1713615277</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5013,6 +5175,7 @@
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5194,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710905979</v>
+        <v>1713619606</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5208,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5227,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710921354</v>
+        <v>1713620234</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5077,6 +5241,7 @@
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5260,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710924365</v>
+        <v>1713659764</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5109,6 +5274,7 @@
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5293,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710924865</v>
+        <v>1713670008</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5307,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5326,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710976368</v>
+        <v>1713671240</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5173,6 +5340,7 @@
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5359,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710983900</v>
+        <v>1713673302</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5205,6 +5373,7 @@
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5392,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710985103</v>
+        <v>1713686877</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5406,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5425,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710987027</v>
+        <v>1713703468</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5269,6 +5439,7 @@
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5458,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710997112</v>
+        <v>1713707906</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5301,6 +5472,7 @@
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5491,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1711010312</v>
+        <v>1713708561</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5505,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5524,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1711013729</v>
+        <v>1713742990</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5365,6 +5538,7 @@
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5557,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1711014125</v>
+        <v>1713744311</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5397,6 +5571,7 @@
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5590,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1711060383</v>
+        <v>1713745317</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5604,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5623,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1711061503</v>
+        <v>1713776811</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5461,6 +5637,7 @@
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5656,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1711062240</v>
+        <v>1713780002</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5493,6 +5670,7 @@
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5689,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1711095966</v>
+        <v>1713780635</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5703,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5722,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1711098256</v>
+        <v>1713830041</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5557,6 +5736,7 @@
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5755,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1711098764</v>
+        <v>1713831435</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5589,6 +5769,7 @@
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5788,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1711146601</v>
+        <v>1713832442</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5802,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5821,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1711147856</v>
+        <v>1713843474</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5653,6 +5835,7 @@
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5854,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1711148610</v>
+        <v>1713849474</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5685,6 +5868,11 @@
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5891,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1711173322</v>
+        <v>1713870877</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +5905,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +5924,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1711175321</v>
+        <v>1713874423</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5749,6 +5938,7 @@
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +5957,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711175736</v>
+        <v>1713875041</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5781,6 +5971,7 @@
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +5990,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711233822</v>
+        <v>1713917075</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6004,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6023,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711235222</v>
+        <v>1713918655</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5845,6 +6037,7 @@
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6056,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711236057</v>
+        <v>1713919496</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5877,6 +6070,7 @@
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6089,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711272112</v>
+        <v>1713948901</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6103,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6122,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711274658</v>
+        <v>1713952288</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5941,6 +6136,7 @@
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6155,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711275234</v>
+        <v>1713952954</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5973,6 +6169,7 @@
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6188,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711320374</v>
+        <v>1714002960</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6202,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6221,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711321763</v>
+        <v>1714004401</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6037,6 +6235,7 @@
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6254,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1711322531</v>
+        <v>1714005356</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6069,6 +6268,7 @@
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6287,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1711347452</v>
+        <v>1714017070</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6301,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6320,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1711349967</v>
+        <v>1714022153</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6133,6 +6334,11 @@
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6357,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1711350538</v>
+        <v>1714039551</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6165,6 +6371,7 @@
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6390,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1711411669</v>
+        <v>1714042391</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6404,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6423,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1711413331</v>
+        <v>1714043065</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6229,6 +6437,7 @@
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6456,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1711414216</v>
+        <v>1714089410</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6261,6 +6470,7 @@
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6489,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1711427149</v>
+        <v>1714090807</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6503,7 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6522,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1711431631</v>
+        <v>1714091841</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6325,6 +6536,7 @@
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6555,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1711456796</v>
+        <v>1714134163</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6357,6 +6569,7 @@
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6588,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1711460105</v>
+        <v>1714137611</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6602,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6621,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1711460694</v>
+        <v>1714138263</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6421,6 +6635,7 @@
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6654,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1711502480</v>
+        <v>1714179730</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6453,6 +6668,7 @@
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6687,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711507234</v>
+        <v>1714186409</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6701,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6720,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711508454</v>
+        <v>1714187547</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6517,6 +6734,7 @@
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6753,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711510888</v>
+        <v>1714189668</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6549,6 +6767,7 @@
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6786,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711525898</v>
+        <v>1714196127</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +6800,7 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6819,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711545874</v>
+        <v>1714226794</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6613,6 +6833,7 @@
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6852,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711550467</v>
+        <v>1714231855</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6645,6 +6866,7 @@
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6885,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711551101</v>
+        <v>1714232589</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6677,6 +6899,7 @@
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +6918,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711588312</v>
+        <v>1714266532</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6709,6 +6932,7 @@
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +6951,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711592900</v>
+        <v>1714278249</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6741,6 +6965,7 @@
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +6984,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711594398</v>
+        <v>1714279621</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +6998,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7017,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711596761</v>
+        <v>1714281930</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6805,6 +7031,7 @@
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7050,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711606146</v>
+        <v>1714292146</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7064,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7083,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711625046</v>
+        <v>1714309065</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6869,6 +7097,7 @@
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7116,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711629992</v>
+        <v>1714313076</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6901,6 +7130,7 @@
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7149,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711630617</v>
+        <v>1714313800</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6933,6 +7163,7 @@
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
